--- a/cross_channel_link_result.xlsx
+++ b/cross_channel_link_result.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andrew\Desktop\боц8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D162CD0F-445F-4F1A-A9AC-29B54E4F0C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{687D34EA-EF1C-4200-BA92-23594777D03E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3480" yWindow="2355" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -421,28 +421,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>0.98560999999999999</v>
+        <v>1.0133430000000001</v>
       </c>
       <c r="C2" s="1">
-        <v>1.84E-4</v>
+        <v>1.92E-4</v>
       </c>
       <c r="D2" s="1">
-        <v>1.37E-4</v>
+        <v>1.85E-4</v>
       </c>
       <c r="E2" s="1">
-        <v>1.95E-4</v>
+        <v>1.5799999999999999E-4</v>
       </c>
       <c r="F2" s="1">
-        <v>1.9699999999999999E-4</v>
+        <v>1.6699999999999999E-4</v>
       </c>
       <c r="G2" s="1">
-        <v>1.3999999999999999E-4</v>
+        <v>1.83E-4</v>
       </c>
       <c r="H2" s="1">
-        <v>1.7200000000000001E-4</v>
+        <v>1.7699999999999999E-4</v>
       </c>
       <c r="I2" s="1">
-        <v>1.54E-4</v>
+        <v>1.5899999999999999E-4</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -450,25 +450,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>1.7000000000000001E-4</v>
+        <v>1.5300000000000001E-4</v>
       </c>
       <c r="C3" s="1">
-        <v>0.98660599999999998</v>
+        <v>1.0164489999999999</v>
       </c>
       <c r="D3" s="1">
-        <v>2.1000000000000001E-4</v>
+        <v>1.76E-4</v>
       </c>
       <c r="E3" s="1">
-        <v>1.55E-4</v>
+        <v>1.7100000000000001E-4</v>
       </c>
       <c r="F3" s="1">
-        <v>1.9900000000000001E-4</v>
+        <v>1.74E-4</v>
       </c>
       <c r="G3" s="1">
-        <v>1.9599999999999999E-4</v>
+        <v>1.5300000000000001E-4</v>
       </c>
       <c r="H3" s="1">
-        <v>2.5300000000000002E-4</v>
+        <v>2.23E-4</v>
       </c>
       <c r="I3" s="1">
         <v>1.65E-4</v>
@@ -479,28 +479,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>1.47E-4</v>
+        <v>1.5799999999999999E-4</v>
       </c>
       <c r="C4" s="1">
-        <v>1.8599999999999999E-4</v>
+        <v>1.63E-4</v>
       </c>
       <c r="D4" s="1">
-        <v>0.984653</v>
+        <v>1.0139050000000001</v>
       </c>
       <c r="E4" s="1">
-        <v>1.95E-4</v>
+        <v>1.6000000000000001E-4</v>
       </c>
       <c r="F4" s="1">
-        <v>1.92E-4</v>
+        <v>2.3499999999999999E-4</v>
       </c>
       <c r="G4" s="1">
-        <v>2.7500000000000002E-4</v>
+        <v>1.65E-4</v>
       </c>
       <c r="H4" s="1">
-        <v>2.23E-4</v>
+        <v>1.7899999999999999E-4</v>
       </c>
       <c r="I4" s="1">
-        <v>1.6000000000000001E-4</v>
+        <v>1.46E-4</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -508,28 +508,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>1.6899999999999999E-4</v>
+        <v>1.7899999999999999E-4</v>
       </c>
       <c r="C5" s="1">
-        <v>1.5300000000000001E-4</v>
+        <v>1.84E-4</v>
       </c>
       <c r="D5" s="1">
-        <v>1.25E-4</v>
+        <v>1.65E-4</v>
       </c>
       <c r="E5" s="1">
-        <v>0.98392000000000002</v>
+        <v>1.0211600000000001</v>
       </c>
       <c r="F5" s="1">
-        <v>8.92E-4</v>
+        <v>1.6699999999999999E-4</v>
       </c>
       <c r="G5" s="1">
-        <v>1.55E-4</v>
+        <v>2.4800000000000001E-4</v>
       </c>
       <c r="H5" s="1">
-        <v>1.6799999999999999E-4</v>
+        <v>1.76E-4</v>
       </c>
       <c r="I5" s="1">
-        <v>1.5799999999999999E-4</v>
+        <v>1.9900000000000001E-4</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -537,28 +537,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>2.0900000000000001E-4</v>
+        <v>1.5899999999999999E-4</v>
       </c>
       <c r="C6" s="1">
-        <v>2.02E-4</v>
+        <v>1.6100000000000001E-4</v>
       </c>
       <c r="D6" s="1">
-        <v>2.0100000000000001E-4</v>
+        <v>2.32E-4</v>
       </c>
       <c r="E6" s="1">
-        <v>8.0099999999999995E-4</v>
+        <v>1.7699999999999999E-4</v>
       </c>
       <c r="F6" s="1">
-        <v>0.98755899999999996</v>
+        <v>1.01292</v>
       </c>
       <c r="G6" s="1">
-        <v>2.6400000000000002E-4</v>
+        <v>1.9100000000000001E-4</v>
       </c>
       <c r="H6" s="1">
-        <v>9.7999999999999997E-5</v>
+        <v>2.4800000000000001E-4</v>
       </c>
       <c r="I6" s="1">
-        <v>1.6100000000000001E-4</v>
+        <v>1.9000000000000001E-4</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -566,28 +566,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>1.5200000000000001E-4</v>
+        <v>1.8799999999999999E-4</v>
       </c>
       <c r="C7" s="1">
-        <v>2.0000000000000001E-4</v>
+        <v>1.7000000000000001E-4</v>
       </c>
       <c r="D7" s="1">
-        <v>2.72E-4</v>
+        <v>2.1100000000000001E-4</v>
       </c>
       <c r="E7" s="1">
-        <v>1.64E-4</v>
+        <v>2.1599999999999999E-4</v>
       </c>
       <c r="F7" s="1">
-        <v>1.4300000000000001E-4</v>
+        <v>2.1699999999999999E-4</v>
       </c>
       <c r="G7" s="1">
-        <v>0.98730799999999996</v>
+        <v>1.018221</v>
       </c>
       <c r="H7" s="1">
-        <v>1.7100000000000001E-4</v>
+        <v>2.0100000000000001E-4</v>
       </c>
       <c r="I7" s="1">
-        <v>1.2799999999999999E-4</v>
+        <v>1.94E-4</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -595,28 +595,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>1.7899999999999999E-4</v>
+        <v>1.6899999999999999E-4</v>
       </c>
       <c r="C8" s="1">
-        <v>2.61E-4</v>
+        <v>1.7799999999999999E-4</v>
       </c>
       <c r="D8" s="1">
-        <v>2.2800000000000001E-4</v>
+        <v>1.7000000000000001E-4</v>
       </c>
       <c r="E8" s="1">
-        <v>1.65E-4</v>
+        <v>1.6799999999999999E-4</v>
       </c>
       <c r="F8" s="1">
-        <v>1.02E-4</v>
+        <v>2.4600000000000002E-4</v>
       </c>
       <c r="G8" s="1">
-        <v>2.34E-4</v>
+        <v>1.6699999999999999E-4</v>
       </c>
       <c r="H8" s="1">
-        <v>0.990317</v>
+        <v>1.0202659999999999</v>
       </c>
       <c r="I8" s="1">
-        <v>1.2300000000000001E-4</v>
+        <v>2.13E-4</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -624,28 +624,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>1.74E-4</v>
+        <v>1.64E-4</v>
       </c>
       <c r="C9" s="1">
-        <v>1.7000000000000001E-4</v>
+        <v>1.92E-4</v>
       </c>
       <c r="D9" s="1">
-        <v>1.63E-4</v>
+        <v>1.5300000000000001E-4</v>
       </c>
       <c r="E9" s="1">
-        <v>1.6200000000000001E-4</v>
+        <v>1.64E-4</v>
       </c>
       <c r="F9" s="1">
-        <v>1.65E-4</v>
+        <v>1.7699999999999999E-4</v>
       </c>
       <c r="G9" s="1">
-        <v>1.4100000000000001E-4</v>
+        <v>1.55E-4</v>
       </c>
       <c r="H9" s="1">
-        <v>1.64E-4</v>
+        <v>2.0799999999999999E-4</v>
       </c>
       <c r="I9" s="1">
-        <v>0.99211700000000003</v>
+        <v>1.026081</v>
       </c>
     </row>
   </sheetData>

--- a/cross_channel_link_result.xlsx
+++ b/cross_channel_link_result.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andrew\Desktop\боц8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{687D34EA-EF1C-4200-BA92-23594777D03E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B6D99C5-30C3-416D-B1DA-7DF8D06664EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2550" yWindow="2550" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -421,28 +421,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>1.0133430000000001</v>
+        <v>0.98365199999999997</v>
       </c>
       <c r="C2" s="1">
-        <v>1.92E-4</v>
+        <v>1.5300000000000001E-4</v>
       </c>
       <c r="D2" s="1">
-        <v>1.85E-4</v>
+        <v>1.4300000000000001E-4</v>
       </c>
       <c r="E2" s="1">
-        <v>1.5799999999999999E-4</v>
+        <v>1.4899999999999999E-4</v>
       </c>
       <c r="F2" s="1">
-        <v>1.6699999999999999E-4</v>
+        <v>1.4100000000000001E-4</v>
       </c>
       <c r="G2" s="1">
-        <v>1.83E-4</v>
+        <v>1.8000000000000001E-4</v>
       </c>
       <c r="H2" s="1">
-        <v>1.7699999999999999E-4</v>
+        <v>1.4300000000000001E-4</v>
       </c>
       <c r="I2" s="1">
-        <v>1.5899999999999999E-4</v>
+        <v>1.55E-4</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -450,28 +450,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
+        <v>1.6000000000000001E-4</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.97478299999999996</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1.21E-4</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1.6200000000000001E-4</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1.3799999999999999E-4</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.3300000000000001E-4</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1.7100000000000001E-4</v>
+      </c>
+      <c r="I3" s="1">
         <v>1.5300000000000001E-4</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1.0164489999999999</v>
-      </c>
-      <c r="D3" s="1">
-        <v>1.76E-4</v>
-      </c>
-      <c r="E3" s="1">
-        <v>1.7100000000000001E-4</v>
-      </c>
-      <c r="F3" s="1">
-        <v>1.74E-4</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.5300000000000001E-4</v>
-      </c>
-      <c r="H3" s="1">
-        <v>2.23E-4</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.65E-4</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -479,28 +479,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>1.5799999999999999E-4</v>
+        <v>1.64E-4</v>
       </c>
       <c r="C4" s="1">
-        <v>1.63E-4</v>
+        <v>1.3300000000000001E-4</v>
       </c>
       <c r="D4" s="1">
-        <v>1.0139050000000001</v>
+        <v>0.97719599999999995</v>
       </c>
       <c r="E4" s="1">
-        <v>1.6000000000000001E-4</v>
+        <v>1.3100000000000001E-4</v>
       </c>
       <c r="F4" s="1">
-        <v>2.3499999999999999E-4</v>
+        <v>2.0100000000000001E-4</v>
       </c>
       <c r="G4" s="1">
-        <v>1.65E-4</v>
+        <v>1.73E-4</v>
       </c>
       <c r="H4" s="1">
-        <v>1.7899999999999999E-4</v>
+        <v>1.46E-4</v>
       </c>
       <c r="I4" s="1">
-        <v>1.46E-4</v>
+        <v>1.4999999999999999E-4</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -508,28 +508,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>1.7899999999999999E-4</v>
+        <v>1.35E-4</v>
       </c>
       <c r="C5" s="1">
-        <v>1.84E-4</v>
+        <v>1.7000000000000001E-4</v>
       </c>
       <c r="D5" s="1">
+        <v>1.47E-4</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.98200299999999996</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1.6200000000000001E-4</v>
+      </c>
+      <c r="G5" s="1">
         <v>1.65E-4</v>
       </c>
-      <c r="E5" s="1">
-        <v>1.0211600000000001</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1.6699999999999999E-4</v>
-      </c>
-      <c r="G5" s="1">
-        <v>2.4800000000000001E-4</v>
-      </c>
       <c r="H5" s="1">
-        <v>1.76E-4</v>
+        <v>1.63E-4</v>
       </c>
       <c r="I5" s="1">
-        <v>1.9900000000000001E-4</v>
+        <v>1.2400000000000001E-4</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -537,28 +537,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>1.5899999999999999E-4</v>
+        <v>1.47E-4</v>
       </c>
       <c r="C6" s="1">
-        <v>1.6100000000000001E-4</v>
+        <v>1.75E-4</v>
       </c>
       <c r="D6" s="1">
-        <v>2.32E-4</v>
+        <v>2.1100000000000001E-4</v>
       </c>
       <c r="E6" s="1">
-        <v>1.7699999999999999E-4</v>
+        <v>1.4899999999999999E-4</v>
       </c>
       <c r="F6" s="1">
-        <v>1.01292</v>
+        <v>0.97676700000000005</v>
       </c>
       <c r="G6" s="1">
-        <v>1.9100000000000001E-4</v>
+        <v>1.4999999999999999E-4</v>
       </c>
       <c r="H6" s="1">
-        <v>2.4800000000000001E-4</v>
+        <v>2.31E-4</v>
       </c>
       <c r="I6" s="1">
-        <v>1.9000000000000001E-4</v>
+        <v>1.6699999999999999E-4</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -566,28 +566,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
+        <v>1.8900000000000001E-4</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1.22E-4</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1.8200000000000001E-4</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1.73E-4</v>
+      </c>
+      <c r="F7" s="1">
         <v>1.8799999999999999E-4</v>
       </c>
-      <c r="C7" s="1">
-        <v>1.7000000000000001E-4</v>
-      </c>
-      <c r="D7" s="1">
-        <v>2.1100000000000001E-4</v>
-      </c>
-      <c r="E7" s="1">
-        <v>2.1599999999999999E-4</v>
-      </c>
-      <c r="F7" s="1">
-        <v>2.1699999999999999E-4</v>
-      </c>
       <c r="G7" s="1">
-        <v>1.018221</v>
+        <v>0.97648999999999997</v>
       </c>
       <c r="H7" s="1">
-        <v>2.0100000000000001E-4</v>
+        <v>1.63E-4</v>
       </c>
       <c r="I7" s="1">
-        <v>1.94E-4</v>
+        <v>1.54E-4</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -595,28 +595,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>1.6899999999999999E-4</v>
+        <v>1.36E-4</v>
       </c>
       <c r="C8" s="1">
         <v>1.7799999999999999E-4</v>
       </c>
       <c r="D8" s="1">
-        <v>1.7000000000000001E-4</v>
+        <v>1.55E-4</v>
       </c>
       <c r="E8" s="1">
-        <v>1.6799999999999999E-4</v>
+        <v>1.44E-4</v>
       </c>
       <c r="F8" s="1">
-        <v>2.4600000000000002E-4</v>
+        <v>2.2100000000000001E-4</v>
       </c>
       <c r="G8" s="1">
-        <v>1.6699999999999999E-4</v>
+        <v>1.4899999999999999E-4</v>
       </c>
       <c r="H8" s="1">
-        <v>1.0202659999999999</v>
+        <v>0.98038000000000003</v>
       </c>
       <c r="I8" s="1">
-        <v>2.13E-4</v>
+        <v>1.7799999999999999E-4</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -624,28 +624,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>1.64E-4</v>
+        <v>1.5200000000000001E-4</v>
       </c>
       <c r="C9" s="1">
-        <v>1.92E-4</v>
+        <v>1.66E-4</v>
       </c>
       <c r="D9" s="1">
-        <v>1.5300000000000001E-4</v>
+        <v>1.4799999999999999E-4</v>
       </c>
       <c r="E9" s="1">
         <v>1.64E-4</v>
       </c>
       <c r="F9" s="1">
-        <v>1.7699999999999999E-4</v>
+        <v>1.75E-4</v>
       </c>
       <c r="G9" s="1">
-        <v>1.55E-4</v>
+        <v>1.46E-4</v>
       </c>
       <c r="H9" s="1">
-        <v>2.0799999999999999E-4</v>
+        <v>1.7200000000000001E-4</v>
       </c>
       <c r="I9" s="1">
-        <v>1.026081</v>
+        <v>0.97774499999999998</v>
       </c>
     </row>
   </sheetData>
